--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post FET_HRM-2031-0232/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post FET_HRM-2031-0232/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.28169</v>
+        <v>18.0617</v>
       </c>
       <c r="D2" t="n">
-        <v>17.7027</v>
+        <v>17.3334</v>
       </c>
       <c r="E2" t="n">
-        <v>17.54676</v>
+        <v>17.54022</v>
       </c>
       <c r="F2" t="n">
-        <v>44.23216</v>
+        <v>44.43301</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05333</v>
+        <v>0.05292</v>
       </c>
       <c r="H2" t="n">
-        <v>1.91642</v>
+        <v>1.91615</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.60637</v>
+        <v>17.43851</v>
       </c>
       <c r="D3" t="n">
-        <v>17.46514</v>
+        <v>16.94815</v>
       </c>
       <c r="E3" t="n">
-        <v>17.36628</v>
+        <v>17.3794</v>
       </c>
       <c r="F3" t="n">
-        <v>43.89021</v>
+        <v>43.74376</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05194</v>
+        <v>0.05365</v>
       </c>
       <c r="H3" t="n">
-        <v>1.87284</v>
+        <v>1.88848</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.36832</v>
+        <v>17.5564</v>
       </c>
       <c r="D4" t="n">
-        <v>17.4726</v>
+        <v>17.34652</v>
       </c>
       <c r="E4" t="n">
-        <v>17.28758</v>
+        <v>17.46787</v>
       </c>
       <c r="F4" t="n">
-        <v>45.47921</v>
+        <v>44.91481</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05394</v>
+        <v>0.05323</v>
       </c>
       <c r="H4" t="n">
-        <v>1.90864</v>
+        <v>1.87856</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.28256</v>
+        <v>17.28595</v>
       </c>
       <c r="D6" t="n">
-        <v>16.85341</v>
+        <v>16.66461</v>
       </c>
       <c r="E6" t="n">
-        <v>17.04556</v>
+        <v>16.82123</v>
       </c>
       <c r="F6" t="n">
-        <v>22.95827</v>
+        <v>22.47417</v>
       </c>
       <c r="G6" t="n">
-        <v>35.34044</v>
+        <v>35.72824</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.33682</v>
+        <v>17.51823</v>
       </c>
       <c r="D7" t="n">
-        <v>16.42196</v>
+        <v>16.66105</v>
       </c>
       <c r="E7" t="n">
-        <v>17.31803</v>
+        <v>17.24801</v>
       </c>
       <c r="F7" t="n">
-        <v>23.60019</v>
+        <v>22.84355</v>
       </c>
       <c r="G7" t="n">
-        <v>35.54445</v>
+        <v>35.41768</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.20242</v>
+        <v>17.50834</v>
       </c>
       <c r="D8" t="n">
-        <v>16.71727</v>
+        <v>17.02622</v>
       </c>
       <c r="E8" t="n">
-        <v>16.94713</v>
+        <v>17.04143</v>
       </c>
       <c r="F8" t="n">
-        <v>22.30372</v>
+        <v>22.22575</v>
       </c>
       <c r="G8" t="n">
-        <v>36.11872</v>
+        <v>36.48649</v>
       </c>
     </row>
   </sheetData>
